--- a/data/trans_camb/P13_R-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P13_R-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 4,09</t>
+          <t>-0,44; 4,22</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 2,98</t>
+          <t>-1,67; 2,91</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,97; 10,29</t>
+          <t>3,97; 9,83</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,33; 10,24</t>
+          <t>5,48; 10,38</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,24; 6,11</t>
+          <t>1,11; 6,08</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,37; 13,5</t>
+          <t>8,15; 12,88</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,7; 7,18</t>
+          <t>3,58; 7,2</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,54; 3,91</t>
+          <t>0,5; 4,07</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7,26; 11,15</t>
+          <t>7,31; 11,33</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-4,89; 92,2</t>
+          <t>-7,51; 94,98</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-24,35; 67,91</t>
+          <t>-26,61; 65,45</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>63,29; 221,69</t>
+          <t>65,37; 223,1</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>62,19; 168,22</t>
+          <t>65,65; 170,94</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>12,8; 97,79</t>
+          <t>12,99; 95,06</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>98,2; 220,0</t>
+          <t>99,73; 213,84</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>52,71; 130,8</t>
+          <t>51,7; 129,37</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,42; 67,16</t>
+          <t>7,02; 70,86</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>101,72; 192,75</t>
+          <t>102,68; 206,16</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,38; 2,85</t>
+          <t>0,4; 2,74</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 1,65</t>
+          <t>-0,59; 1,65</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 2,44</t>
+          <t>-0,12; 2,35</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,69; 4,57</t>
+          <t>1,57; 4,58</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 1,51</t>
+          <t>-0,94; 1,6</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 2,34</t>
+          <t>-0,37; 2,32</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,3; 3,15</t>
+          <t>1,38; 3,31</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 1,2</t>
+          <t>-0,44; 1,22</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,14; 2,08</t>
+          <t>0,17; 2,0</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>10,35; 165,84</t>
+          <t>13,53; 161,39</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-16,43; 97,61</t>
+          <t>-20,36; 97,89</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 141,67</t>
+          <t>-3,5; 136,27</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>43,02; 173,47</t>
+          <t>38,24; 172,02</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-24,47; 55,58</t>
+          <t>-23,49; 65,9</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-14,44; 90,01</t>
+          <t>-10,25; 86,44</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>41,83; 138,79</t>
+          <t>41,42; 140,49</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-14,36; 50,11</t>
+          <t>-13,24; 49,63</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,2; 90,07</t>
+          <t>5,07; 84,22</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 2,89</t>
+          <t>-1,17; 3,01</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 2,21</t>
+          <t>-1,33; 2,45</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 3,99</t>
+          <t>-0,14; 3,86</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 2,55</t>
+          <t>-2,92; 2,27</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 2,02</t>
+          <t>-2,73; 2,03</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 0,76</t>
+          <t>-2,97; 0,91</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 2,06</t>
+          <t>-1,36; 2,0</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 1,63</t>
+          <t>-1,48; 1,63</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 1,93</t>
+          <t>-0,89; 1,93</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-43,41; 241,22</t>
+          <t>-45,4; 292,99</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-53,42; 213,38</t>
+          <t>-55,72; 214,71</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-7,91; 332,18</t>
+          <t>-13,3; 328,41</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-52,38; 105,18</t>
+          <t>-60,05; 84,29</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-57,34; 79,92</t>
+          <t>-54,81; 74,47</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-56,54; 30,85</t>
+          <t>-58,43; 36,77</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-33,29; 97,74</t>
+          <t>-38,21; 90,46</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-40,24; 77,28</t>
+          <t>-41,32; 74,59</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-24,76; 93,47</t>
+          <t>-24,69; 91,53</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,46; 2,39</t>
+          <t>0,54; 2,47</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 1,16</t>
+          <t>-0,63; 1,17</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,34; 2,65</t>
+          <t>0,47; 2,67</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,19; 5,6</t>
+          <t>3,2; 5,68</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 1,8</t>
+          <t>-0,28; 1,83</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,62; 3,09</t>
+          <t>0,4; 3,09</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,17; 3,81</t>
+          <t>2,16; 3,74</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 1,23</t>
+          <t>-0,21; 1,2</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,92; 2,7</t>
+          <t>0,97; 2,67</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>12,22; 86,51</t>
+          <t>15,89; 92,37</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-17,98; 42,85</t>
+          <t>-18,05; 40,83</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10,56; 93,79</t>
+          <t>14,27; 97,71</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>59,02; 130,59</t>
+          <t>59,27; 130,62</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-8,37; 40,88</t>
+          <t>-5,59; 42,73</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,12; 71,08</t>
+          <t>8,7; 70,93</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>48,5; 101,8</t>
+          <t>49,29; 102,51</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-4,25; 34,1</t>
+          <t>-4,94; 32,12</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>19,85; 72,01</t>
+          <t>22,25; 71,98</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P13_R-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P13_R-Estudios-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6,88</t>
+          <t>6,09</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,6</t>
+          <t>10,7</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>9,15</t>
+          <t>8,84</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 4,22</t>
+          <t>-0,44; 4,34</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 2,91</t>
+          <t>-1,6; 2,79</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,97; 9,83</t>
+          <t>3,57; 8,99</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,48; 10,38</t>
+          <t>5,66; 10,4</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,11; 6,08</t>
+          <t>1,17; 5,97</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,15; 12,88</t>
+          <t>8,25; 13,01</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,58; 7,2</t>
+          <t>3,61; 6,97</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,5; 4,07</t>
+          <t>0,53; 3,97</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7,31; 11,33</t>
+          <t>7,0; 10,92</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>128,67%</t>
+          <t>113,94%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>148,36%</t>
+          <t>149,78%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>144,0%</t>
+          <t>139,15%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-7,51; 94,98</t>
+          <t>-6,94; 98,06</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-26,61; 65,45</t>
+          <t>-23,17; 63,65</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>65,37; 223,1</t>
+          <t>58,78; 218,49</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>65,65; 170,94</t>
+          <t>67,49; 167,64</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>12,99; 95,06</t>
+          <t>13,68; 94,6</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>99,73; 213,84</t>
+          <t>97,45; 211,81</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>51,7; 129,37</t>
+          <t>50,58; 124,51</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,02; 70,86</t>
+          <t>7,53; 71,21</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>102,68; 206,16</t>
+          <t>97,39; 191,8</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,79</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,05</t>
+          <t>1,73</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1,14</t>
+          <t>1,77</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,4; 2,74</t>
+          <t>0,43; 2,74</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 1,65</t>
+          <t>-0,59; 1,72</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 2,35</t>
+          <t>0,57; 2,95</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,57; 4,58</t>
+          <t>1,66; 4,6</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 1,6</t>
+          <t>-1,01; 1,47</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 2,32</t>
+          <t>0,53; 3,0</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,38; 3,31</t>
+          <t>1,34; 3,23</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 1,22</t>
+          <t>-0,35; 1,27</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,17; 2,0</t>
+          <t>0,92; 2,6</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>52,91%</t>
+          <t>78,65%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>32,38%</t>
+          <t>53,19%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>41,47%</t>
+          <t>64,39%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>13,53; 161,39</t>
+          <t>13,19; 157,02</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-20,36; 97,89</t>
+          <t>-22,34; 100,79</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,5; 136,27</t>
+          <t>17,73; 168,86</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>38,24; 172,02</t>
+          <t>42,38; 179,53</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-23,49; 65,9</t>
+          <t>-25,2; 58,53</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-10,25; 86,44</t>
+          <t>11,08; 118,1</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>41,42; 140,49</t>
+          <t>41,16; 137,34</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-13,24; 49,63</t>
+          <t>-11,84; 52,53</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,07; 84,22</t>
+          <t>29,38; 112,23</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1,9</t>
+          <t>1,84</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-0,94</t>
+          <t>-0,76</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,55</t>
+          <t>0,6</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 3,01</t>
+          <t>-1,06; 3,04</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 2,45</t>
+          <t>-1,47; 2,37</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 3,86</t>
+          <t>-0,12; 3,69</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 2,27</t>
+          <t>-2,97; 2,06</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 2,03</t>
+          <t>-2,99; 2,17</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,97; 0,91</t>
+          <t>-3,08; 1,29</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 2,0</t>
+          <t>-1,46; 1,95</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 1,63</t>
+          <t>-1,43; 1,53</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 1,93</t>
+          <t>-0,92; 1,79</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-24,47%</t>
+          <t>-19,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>21,25%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-45,4; 292,99</t>
+          <t>-43,62; 268,96</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-55,72; 214,71</t>
+          <t>-56,3; 218,46</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-13,3; 328,41</t>
+          <t>-9,67; 336,93</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-60,05; 84,29</t>
+          <t>-57,15; 73,33</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-54,81; 74,47</t>
+          <t>-57,32; 93,58</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-58,43; 36,77</t>
+          <t>-53,22; 60,31</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-38,21; 90,46</t>
+          <t>-40,69; 93,95</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-41,32; 74,59</t>
+          <t>-41,21; 71,25</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-24,69; 91,53</t>
+          <t>-26,05; 86,01</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1,67</t>
+          <t>2,03</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,97</t>
+          <t>2,58</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1,83</t>
+          <t>2,33</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,54; 2,47</t>
+          <t>0,5; 2,5</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 1,17</t>
+          <t>-0,7; 1,17</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,47; 2,67</t>
+          <t>1,04; 3,04</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,2; 5,68</t>
+          <t>3,15; 5,64</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 1,83</t>
+          <t>-0,49; 1,75</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,4; 3,09</t>
+          <t>1,5; 3,54</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,16; 3,74</t>
+          <t>2,14; 3,77</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 1,2</t>
+          <t>-0,19; 1,24</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,97; 2,67</t>
+          <t>1,62; 3,03</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>52,29%</t>
+          <t>63,78%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>40,63%</t>
+          <t>53,29%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>45,48%</t>
+          <t>57,72%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>15,89; 92,37</t>
+          <t>14,26; 93,03</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-18,05; 40,83</t>
+          <t>-18,96; 42,68</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>14,27; 97,71</t>
+          <t>27,76; 110,46</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>59,27; 130,62</t>
+          <t>58,42; 134,75</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-5,59; 42,73</t>
+          <t>-9,61; 39,86</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,7; 70,93</t>
+          <t>26,65; 82,44</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>49,29; 102,51</t>
+          <t>49,76; 102,39</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-4,94; 32,12</t>
+          <t>-4,53; 32,52</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>22,25; 71,98</t>
+          <t>35,69; 83,59</t>
         </is>
       </c>
     </row>
